--- a/data/trans_orig/P36B16-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P36B16-Provincia-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>863</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,57 +735,57 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5622</t>
+          <t>4406</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1008</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3197</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
           <t>0,32%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,8%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3808</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2083</t>
+          <t>1871</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>493</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6378</t>
+          <t>5591</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6335</t>
+          <t>5447</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>2494</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13467</t>
+          <t>12255</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9029</t>
+          <t>6561</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>2517</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27831</t>
+          <t>18604</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>15364</t>
+          <t>12008</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>6450</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34793</t>
+          <t>23215</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>189402</t>
+          <t>177280</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>167396</t>
+          <t>158180</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>210756</t>
+          <t>194084</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>55,6%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>49,61%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>67,67%</t>
+          <t>60,87%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>175897</t>
+          <t>180377</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>159078</t>
+          <t>165677</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>190495</t>
+          <t>194036</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>60,73%</t>
+          <t>57,07%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>52,42%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>61,39%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>365298</t>
+          <t>357657</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>337043</t>
+          <t>334756</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>390004</t>
+          <t>380658</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>60,77%</t>
+          <t>56,33%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>52,73%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>59,96%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>108160</t>
+          <t>128524</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>88652</t>
+          <t>111153</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>128711</t>
+          <t>147814</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>40,31%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>46,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>100922</t>
+          <t>124636</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>87123</t>
+          <t>110709</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>115429</t>
+          <t>139552</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>39,43%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>44,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>209081</t>
+          <t>253160</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>185121</t>
+          <t>230049</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>236525</t>
+          <t>277303</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>43,68%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>6548</t>
+          <t>6731</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2858</t>
+          <t>3038</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13483</t>
+          <t>13279</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2702</t>
+          <t>3480</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1158</t>
+          <t>1458</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5671</t>
+          <t>6858</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>9250</t>
+          <t>10211</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4932</t>
+          <t>5796</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>15190</t>
+          <t>17134</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2808</t>
+          <t>2759</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8911</t>
+          <t>9781</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,22 +1442,22 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3777</t>
+          <t>3776</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1350</t>
+          <t>1425</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8893</t>
+          <t>8917</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>6585</t>
+          <t>6535</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2765</t>
+          <t>2711</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13969</t>
+          <t>13484</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>60022</t>
+          <t>61094</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>43566</t>
+          <t>44323</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>83296</t>
+          <t>81725</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>60497</t>
+          <t>63222</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>48723</t>
+          <t>50060</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>73402</t>
+          <t>77927</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>120519</t>
+          <t>124316</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>100787</t>
+          <t>103913</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>145643</t>
+          <t>148065</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>13,75%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>377746</t>
+          <t>389894</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>344175</t>
+          <t>360770</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>403644</t>
+          <t>413596</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>73,48%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>66,39%</t>
+          <t>67,99%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>77,86%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>359434</t>
+          <t>379426</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>340702</t>
+          <t>359183</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>378525</t>
+          <t>398979</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>69,8%</t>
+          <t>69,43%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>66,16%</t>
+          <t>65,73%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>73,01%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>737179</t>
+          <t>769319</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>704160</t>
+          <t>735328</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>769818</t>
+          <t>798708</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>71,34%</t>
+          <t>71,42%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>68,27%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>74,5%</t>
+          <t>74,15%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>77814</t>
+          <t>76900</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>59708</t>
+          <t>57209</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>106595</t>
+          <t>103084</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>89937</t>
+          <t>98751</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>74536</t>
+          <t>81839</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>107220</t>
+          <t>116709</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>167751</t>
+          <t>175651</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>141645</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>196454</t>
+          <t>204354</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>18,97%</t>
         </is>
       </c>
     </row>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1325</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4861</t>
+          <t>4618</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1325</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
@@ -1939,12 +1939,12 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4214</t>
+          <t>4327</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>7767</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4030</t>
+          <t>4210</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14960</t>
+          <t>14878</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6671</t>
+          <t>7151</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3436</t>
+          <t>3817</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13116</t>
+          <t>12614</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>14821</t>
+          <t>14918</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9630</t>
+          <t>9527</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23034</t>
+          <t>22204</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>22375</t>
+          <t>21973</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15055</t>
+          <t>15226</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>32223</t>
+          <t>31384</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>32747</t>
+          <t>31071</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>24659</t>
+          <t>22975</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>43599</t>
+          <t>41074</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>55121</t>
+          <t>53044</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>43733</t>
+          <t>41699</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>69814</t>
+          <t>65868</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>9,85%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>227355</t>
+          <t>227263</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>211182</t>
+          <t>210318</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>242247</t>
+          <t>241360</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>71,92%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>66,82%</t>
+          <t>66,56%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>76,65%</t>
+          <t>76,38%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>252031</t>
+          <t>259243</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>237657</t>
+          <t>243821</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>265010</t>
+          <t>270957</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>73,53%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>76,85%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>479386</t>
+          <t>486508</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>458050</t>
+          <t>464797</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>499861</t>
+          <t>505972</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>69,25%</t>
+          <t>69,52%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>75,57%</t>
+          <t>75,68%</t>
         </is>
       </c>
     </row>
@@ -2428,27 +2428,27 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>53008</t>
+          <t>53265</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>40811</t>
+          <t>41235</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>66355</t>
+          <t>66350</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>49801</t>
+          <t>51086</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>39851</t>
+          <t>41988</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>61007</t>
+          <t>63410</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>102809</t>
+          <t>104351</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>85417</t>
+          <t>88041</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>120697</t>
+          <t>121424</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,16%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>5162</t>
+          <t>5725</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>2566</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11648</t>
+          <t>12489</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>4137</t>
+          <t>4034</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1214</t>
+          <t>1146</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9989</t>
+          <t>10050</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>9300</t>
+          <t>9759</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5094</t>
+          <t>5002</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>17074</t>
+          <t>17608</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>345387</t>
+          <t>352585</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>345387</t>
+          <t>352585</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>345387</t>
+          <t>352585</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>661437</t>
+          <t>668579</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>661437</t>
+          <t>668579</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>661437</t>
+          <t>668579</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>588</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2781,12 +2781,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>2687</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>2555</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13899</t>
+          <t>15421</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>5795</t>
+          <t>7748</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2259</t>
+          <t>3006</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>14442</t>
+          <t>16635</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>63694</t>
+          <t>70713</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>49104</t>
+          <t>54905</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>81627</t>
+          <t>89245</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>108318</t>
+          <t>121988</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>64267</t>
+          <t>104282</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>139638</t>
+          <t>140622</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>172012</t>
+          <t>192701</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>123481</t>
+          <t>167088</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>206203</t>
+          <t>219366</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>27,59%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>217229</t>
+          <t>263429</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>196011</t>
+          <t>239378</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>236804</t>
+          <t>285194</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>69,5%</t>
+          <t>70,6%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>64,15%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>259765</t>
+          <t>254158</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>153580</t>
+          <t>233595</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>314943</t>
+          <t>274589</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>60,23%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>55,36%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>66,2%</t>
+          <t>65,07%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>476993</t>
+          <t>517588</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>347656</t>
+          <t>486106</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>534687</t>
+          <t>546600</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>60,51%</t>
+          <t>65,1%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>61,14%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>68,75%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>27913</t>
+          <t>34666</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>16797</t>
+          <t>20451</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>42585</t>
+          <t>52333</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>102425</t>
+          <t>38655</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>34612</t>
+          <t>28808</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>254526</t>
+          <t>50577</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>130337</t>
+          <t>73321</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>61925</t>
+          <t>56529</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>308535</t>
+          <t>95195</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>11,97%</t>
         </is>
       </c>
     </row>
@@ -3223,7 +3223,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3138</t>
+          <t>3749</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>15452</t>
+          <t>20894</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>3138</t>
+          <t>3749</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
@@ -3303,12 +3303,12 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>16207</t>
+          <t>18729</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>543</t>
+          <t>595</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2740</t>
+          <t>3025</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>543</t>
+          <t>595</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2212</t>
+          <t>3050</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -3566,32 +3566,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>12169</t>
+          <t>13718</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>7776</t>
+          <t>8556</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>18649</t>
+          <t>21002</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>24062</t>
+          <t>24407</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>18338</t>
+          <t>18304</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>31409</t>
+          <t>31995</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>36231</t>
+          <t>38125</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>28124</t>
+          <t>30379</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>45495</t>
+          <t>48905</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,31%</t>
         </is>
       </c>
     </row>
@@ -3679,32 +3679,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>142861</t>
+          <t>161579</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>132508</t>
+          <t>148896</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>151753</t>
+          <t>170891</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>72,4%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>83,09%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>163419</t>
+          <t>179576</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>154550</t>
+          <t>169050</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>171140</t>
+          <t>187482</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>78,46%</t>
+          <t>79,17%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>74,21%</t>
+          <t>74,53%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>306279</t>
+          <t>341155</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>293180</t>
+          <t>325967</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>317906</t>
+          <t>353682</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>78,88%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>75,75%</t>
+          <t>75,37%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>81,78%</t>
         </is>
       </c>
     </row>
@@ -3792,32 +3792,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>21808</t>
+          <t>28414</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>14150</t>
+          <t>19634</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>31252</t>
+          <t>39668</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,32 +3827,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>20382</t>
+          <t>22408</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>15231</t>
+          <t>16966</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>26912</t>
+          <t>29802</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>42189</t>
+          <t>50822</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>33037</t>
+          <t>40599</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>53567</t>
+          <t>64214</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,85%</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>1361</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>6645</t>
+          <t>7589</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>432</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -3950,12 +3950,12 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2236</t>
+          <t>2366</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>1774</t>
+          <t>1791</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
@@ -3985,12 +3985,12 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>7442</t>
+          <t>8386</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>995</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -4145,12 +4145,12 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>3582</t>
+          <t>3455</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4170,22 +4170,22 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>1428</t>
+          <t>1443</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>381</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>4394</t>
+          <t>4168</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,22 +4205,22 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>2464</t>
+          <t>2438</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>923</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>5955</t>
+          <t>5409</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -4248,32 +4248,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>21907</t>
+          <t>22640</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>15737</t>
+          <t>16600</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>31027</t>
+          <t>31427</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4283,32 +4283,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>22646</t>
+          <t>24342</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>16418</t>
+          <t>18014</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>29520</t>
+          <t>31890</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>44553</t>
+          <t>46982</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>34785</t>
+          <t>37508</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>55663</t>
+          <t>58627</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,99%</t>
         </is>
       </c>
     </row>
@@ -4361,32 +4361,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>192230</t>
+          <t>192290</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>176312</t>
+          <t>177387</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>205083</t>
+          <t>205133</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>71,03%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>65,39%</t>
+          <t>65,53%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4396,32 +4396,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>196493</t>
+          <t>200070</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>184018</t>
+          <t>188382</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>206298</t>
+          <t>209864</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>76,7%</t>
+          <t>76,1%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,32 +4431,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>388723</t>
+          <t>392360</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>370897</t>
+          <t>372608</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>405874</t>
+          <t>408806</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>73,53%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>69,83%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>76,61%</t>
         </is>
       </c>
     </row>
@@ -4474,32 +4474,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>53579</t>
+          <t>53912</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>41926</t>
+          <t>43185</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>68301</t>
+          <t>68263</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4509,32 +4509,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>34249</t>
+          <t>35680</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>26178</t>
+          <t>27483</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>45341</t>
+          <t>45624</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,32 +4544,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>87828</t>
+          <t>89592</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>73662</t>
+          <t>74607</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>105710</t>
+          <t>108149</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,27%</t>
         </is>
       </c>
     </row>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>869</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>4592</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -4612,7 +4612,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>1364</t>
+          <t>1366</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -4632,12 +4632,12 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>4822</t>
+          <t>4905</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,22 +4657,22 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>2248</t>
+          <t>2235</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>615</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>6391</t>
+          <t>6230</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -4700,17 +4700,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>256180</t>
+          <t>262901</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>256180</t>
+          <t>262901</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>256180</t>
+          <t>262901</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>525816</t>
+          <t>533608</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>525816</t>
+          <t>533608</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>525816</t>
+          <t>533608</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4817,32 +4817,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>12023</t>
+          <t>17409</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>6014</t>
+          <t>9326</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>22544</t>
+          <t>30070</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4852,32 +4852,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>16094</t>
+          <t>19802</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>6635</t>
+          <t>13392</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>26060</t>
+          <t>27593</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,32 +4887,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>28117</t>
+          <t>37212</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>16567</t>
+          <t>26432</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>39887</t>
+          <t>51335</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -4930,32 +4930,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>60801</t>
+          <t>71024</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>47022</t>
+          <t>53025</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>80517</t>
+          <t>90253</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4965,32 +4965,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>57355</t>
+          <t>70142</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>27603</t>
+          <t>56676</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>82300</t>
+          <t>84322</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>118156</t>
+          <t>141167</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>79206</t>
+          <t>119367</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>149534</t>
+          <t>167762</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>11,25%</t>
         </is>
       </c>
     </row>
@@ -5043,32 +5043,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>271237</t>
+          <t>308373</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>243317</t>
+          <t>279740</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>300212</t>
+          <t>344430</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>47,86%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5078,32 +5078,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>299269</t>
+          <t>349659</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>146651</t>
+          <t>323979</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>403565</t>
+          <t>374797</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>45,34%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>42,01%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>570506</t>
+          <t>658032</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>368625</t>
+          <t>616872</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>673129</t>
+          <t>699855</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>44,14%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>41,38%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>46,94%</t>
         </is>
       </c>
     </row>
@@ -5156,32 +5156,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>252283</t>
+          <t>286838</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>225448</t>
+          <t>256748</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>283894</t>
+          <t>320358</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5191,32 +5191,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>445703</t>
+          <t>287767</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>306907</t>
+          <t>264563</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>648385</t>
+          <t>314038</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>52,53%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>76,42%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>697986</t>
+          <t>574606</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>562440</t>
+          <t>533249</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>962386</t>
+          <t>613454</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>41,15%</t>
         </is>
       </c>
     </row>
@@ -5269,32 +5269,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>27936</t>
+          <t>36042</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>18364</t>
+          <t>23696</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>40819</t>
+          <t>53602</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5304,32 +5304,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>29983</t>
+          <t>43788</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>13717</t>
+          <t>32054</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>45821</t>
+          <t>58855</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>57920</t>
+          <t>79830</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>35903</t>
+          <t>62502</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>77845</t>
+          <t>103225</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>6,92%</t>
         </is>
       </c>
     </row>
@@ -5382,17 +5382,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5417,17 +5417,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>848405</t>
+          <t>771159</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>848405</t>
+          <t>771159</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>848405</t>
+          <t>771159</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>1472684</t>
+          <t>1490846</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>1472684</t>
+          <t>1490846</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>1472684</t>
+          <t>1490846</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5499,7 +5499,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>1958</t>
+          <t>2117</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -5509,12 +5509,12 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>6941</t>
+          <t>7487</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5534,32 +5534,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>2442</t>
+          <t>2698</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>606</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>5914</t>
+          <t>6505</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5569,32 +5569,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>4400</t>
+          <t>4815</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>1444</t>
+          <t>1756</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>9145</t>
+          <t>10009</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,61%</t>
         </is>
       </c>
     </row>
@@ -5612,32 +5612,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>17428</t>
+          <t>21868</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>6508</t>
+          <t>13960</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>29394</t>
+          <t>32363</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5647,32 +5647,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>41846</t>
+          <t>42110</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>32333</t>
+          <t>32049</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>59412</t>
+          <t>53980</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5682,32 +5682,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>59273</t>
+          <t>63978</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>36276</t>
+          <t>49747</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>81883</t>
+          <t>79452</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -5725,32 +5725,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>290497</t>
+          <t>342622</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>129974</t>
+          <t>309750</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>403573</t>
+          <t>369870</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5760,32 +5760,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>307351</t>
+          <t>357428</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>284736</t>
+          <t>330353</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>328455</t>
+          <t>383953</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>42,99%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>39,74%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>46,19%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5795,32 +5795,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>597848</t>
+          <t>700051</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>379488</t>
+          <t>664989</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>713572</t>
+          <t>738687</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>40,81%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>45,33%</t>
         </is>
       </c>
     </row>
@@ -5838,32 +5838,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>351912</t>
+          <t>404414</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>157948</t>
+          <t>377998</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>490991</t>
+          <t>436139</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>50,67%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>52,87%</t>
+          <t>54,65%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5873,32 +5873,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>352590</t>
+          <t>413800</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>331378</t>
+          <t>390068</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>375186</t>
+          <t>441511</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>49,78%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>46,92%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>52,27%</t>
+          <t>53,11%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5908,32 +5908,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>704503</t>
+          <t>818214</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>440313</t>
+          <t>777794</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>842374</t>
+          <t>855730</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>42,79%</t>
+          <t>50,22%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>52,52%</t>
         </is>
       </c>
     </row>
@@ -5951,32 +5951,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>266925</t>
+          <t>27050</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>24940</t>
+          <t>16468</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>632936</t>
+          <t>42008</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>68,15%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5986,67 +5986,67 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>13502</t>
+          <t>15295</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>8445</t>
+          <t>9754</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>21029</t>
+          <t>24604</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
+          <t>1,84%</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>1,17%</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>2,96%</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr">
+        <is>
+          <t>42345</t>
+        </is>
+      </c>
+      <c r="S50" s="2" t="inlineStr">
+        <is>
+          <t>30683</t>
+        </is>
+      </c>
+      <c r="T50" s="2" t="inlineStr">
+        <is>
+          <t>60290</t>
+        </is>
+      </c>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
           <t>1,88%</t>
         </is>
       </c>
-      <c r="O50" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="P50" s="2" t="inlineStr">
-        <is>
-          <t>2,93%</t>
-        </is>
-      </c>
-      <c r="Q50" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="R50" s="2" t="inlineStr">
-        <is>
-          <t>280427</t>
-        </is>
-      </c>
-      <c r="S50" s="2" t="inlineStr">
-        <is>
-          <t>36920</t>
-        </is>
-      </c>
-      <c r="T50" s="2" t="inlineStr">
-        <is>
-          <t>789464</t>
-        </is>
-      </c>
-      <c r="U50" s="2" t="inlineStr">
-        <is>
-          <t>17,03%</t>
-        </is>
-      </c>
-      <c r="V50" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -6064,17 +6064,17 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6099,17 +6099,17 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6134,17 +6134,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6181,32 +6181,32 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>28097</t>
+          <t>33094</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>17911</t>
+          <t>22691</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>41885</t>
+          <t>49151</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6216,32 +6216,32 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>36710</t>
+          <t>43037</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>26285</t>
+          <t>32958</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>50782</t>
+          <t>57572</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6251,32 +6251,32 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>64807</t>
+          <t>76132</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>49422</t>
+          <t>59512</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>82907</t>
+          <t>95583</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -6294,32 +6294,32 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>264731</t>
+          <t>288477</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>209287</t>
+          <t>253624</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>305810</t>
+          <t>328688</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6329,32 +6329,32 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>356498</t>
+          <t>383844</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>288961</t>
+          <t>353292</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>400882</t>
+          <t>416772</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6364,32 +6364,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>621230</t>
+          <t>672321</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>537359</t>
+          <t>626851</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>688465</t>
+          <t>725902</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>10,0%</t>
         </is>
       </c>
     </row>
@@ -6407,32 +6407,32 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>1908556</t>
+          <t>2062732</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>1478008</t>
+          <t>1999908</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>2075082</t>
+          <t>2130598</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>55,16%</t>
+          <t>58,39%</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>56,61%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>59,98%</t>
+          <t>60,31%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6442,67 +6442,67 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>2013657</t>
+          <t>2159939</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>1622787</t>
+          <t>2106401</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>2165061</t>
+          <t>2217038</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>57,92%</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
+          <t>59,45%</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>5186</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr">
+        <is>
+          <t>4222671</t>
+        </is>
+      </c>
+      <c r="S54" s="2" t="inlineStr">
+        <is>
+          <t>4129249</t>
+        </is>
+      </c>
+      <c r="T54" s="2" t="inlineStr">
+        <is>
+          <t>4300041</t>
+        </is>
+      </c>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>58,15%</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>56,86%</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
           <t>59,21%</t>
-        </is>
-      </c>
-      <c r="Q54" s="2" t="inlineStr">
-        <is>
-          <t>5186</t>
-        </is>
-      </c>
-      <c r="R54" s="2" t="inlineStr">
-        <is>
-          <t>3922213</t>
-        </is>
-      </c>
-      <c r="S54" s="2" t="inlineStr">
-        <is>
-          <t>3370567</t>
-        </is>
-      </c>
-      <c r="T54" s="2" t="inlineStr">
-        <is>
-          <t>4191834</t>
-        </is>
-      </c>
-      <c r="U54" s="2" t="inlineStr">
-        <is>
-          <t>55,12%</t>
-        </is>
-      </c>
-      <c r="V54" s="2" t="inlineStr">
-        <is>
-          <t>47,37%</t>
-        </is>
-      </c>
-      <c r="W54" s="2" t="inlineStr">
-        <is>
-          <t>58,91%</t>
         </is>
       </c>
     </row>
@@ -6520,32 +6520,32 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>946477</t>
+          <t>1066933</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>742508</t>
+          <t>1008272</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>1039801</t>
+          <t>1128449</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6555,32 +6555,32 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>1196008</t>
+          <t>1072784</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>1009956</t>
+          <t>1024179</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>1653539</t>
+          <t>1121302</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6590,32 +6590,32 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>2142484</t>
+          <t>2139717</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>1905098</t>
+          <t>2061876</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>2638603</t>
+          <t>2223976</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>30,62%</t>
         </is>
       </c>
     </row>
@@ -6633,32 +6633,32 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>311956</t>
+          <t>81526</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>66134</t>
+          <t>63313</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>1005545</t>
+          <t>108949</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6668,32 +6668,32 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>53426</t>
+          <t>69713</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>39924</t>
+          <t>56148</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>69532</t>
+          <t>88744</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6703,32 +6703,32 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>365382</t>
+          <t>151238</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>116360</t>
+          <t>125158</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>1245530</t>
+          <t>179587</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -6746,17 +6746,17 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6781,17 +6781,17 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>3656299</t>
+          <t>3729317</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>3656299</t>
+          <t>3729317</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>3656299</t>
+          <t>3729317</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6816,17 +6816,17 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>7116116</t>
+          <t>7262079</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>7116116</t>
+          <t>7262079</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>7116116</t>
+          <t>7262079</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
